--- a/artfynd/A 34280-2026 artfynd.xlsx
+++ b/artfynd/A 34280-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136407388</v>
       </c>
       <c r="B2" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136405159</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>136408636</v>
       </c>
       <c r="B26" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>136408641</v>
       </c>
       <c r="B27" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>136408673</v>
       </c>
       <c r="B28" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>136408778</v>
       </c>
       <c r="B29" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34280-2026 artfynd.xlsx
+++ b/artfynd/A 34280-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136407388</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136405159</v>
       </c>
       <c r="B3" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>136408636</v>
       </c>
       <c r="B26" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>136408641</v>
       </c>
       <c r="B27" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>136408673</v>
       </c>
       <c r="B28" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>136408778</v>
       </c>
       <c r="B29" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34280-2026 artfynd.xlsx
+++ b/artfynd/A 34280-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136407388</v>
       </c>
       <c r="B2" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136405159</v>
       </c>
       <c r="B3" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>136405803</v>
       </c>
       <c r="B4" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136407033</v>
       </c>
       <c r="B5" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>136407363</v>
       </c>
       <c r="B6" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>136407810</v>
       </c>
       <c r="B7" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>136408042</v>
       </c>
       <c r="B8" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>136408138</v>
       </c>
       <c r="B9" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>136408393</v>
       </c>
       <c r="B10" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>136409613</v>
       </c>
       <c r="B11" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>136412164</v>
       </c>
       <c r="B12" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>136412874</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>136412943</v>
       </c>
       <c r="B14" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136407329</v>
       </c>
       <c r="B15" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>136407928</v>
       </c>
       <c r="B16" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>136407998</v>
       </c>
       <c r="B17" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136408837</v>
       </c>
       <c r="B18" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136409421</v>
       </c>
       <c r="B19" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>136409568</v>
       </c>
       <c r="B20" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136411323</v>
       </c>
       <c r="B21" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>136414831</v>
       </c>
       <c r="B22" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>136408636</v>
       </c>
       <c r="B26" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>136408641</v>
       </c>
       <c r="B27" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>136408673</v>
       </c>
       <c r="B28" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>136408778</v>
       </c>
       <c r="B29" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34280-2026 artfynd.xlsx
+++ b/artfynd/A 34280-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136407388</v>
       </c>
       <c r="B2" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136405159</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>136408636</v>
       </c>
       <c r="B26" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>136408641</v>
       </c>
       <c r="B27" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>136408673</v>
       </c>
       <c r="B28" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>136408778</v>
       </c>
       <c r="B29" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34280-2026 artfynd.xlsx
+++ b/artfynd/A 34280-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136407388</v>
       </c>
       <c r="B2" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136405159</v>
       </c>
       <c r="B3" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>136408636</v>
       </c>
       <c r="B26" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>136408641</v>
       </c>
       <c r="B27" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>136408673</v>
       </c>
       <c r="B28" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>136408778</v>
       </c>
       <c r="B29" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34280-2026 artfynd.xlsx
+++ b/artfynd/A 34280-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136407388</v>
       </c>
       <c r="B2" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136405159</v>
       </c>
       <c r="B3" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>136408636</v>
       </c>
       <c r="B26" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>136408641</v>
       </c>
       <c r="B27" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>136408673</v>
       </c>
       <c r="B28" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>136408778</v>
       </c>
       <c r="B29" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34280-2026 artfynd.xlsx
+++ b/artfynd/A 34280-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136407388</v>
       </c>
       <c r="B2" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136405159</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>136408636</v>
       </c>
       <c r="B26" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>136408641</v>
       </c>
       <c r="B27" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>136408673</v>
       </c>
       <c r="B28" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>136408778</v>
       </c>
       <c r="B29" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
